--- a/reports/一级子公司A_利润表_2025-07.xlsx
+++ b/reports/一级子公司A_利润表_2025-07.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>190854863</v>
+        <v>196390398</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>185926540</v>
+        <v>187266441</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>1157398331</v>
+        <v>1157584391</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>762992</v>
+        <v>758234</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>4717386</v>
+        <v>4720835</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>664173</v>
+        <v>657350</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>4094966</v>
+        <v>4095501</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>560798</v>
+        <v>557127</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>3468650</v>
+        <v>3470192</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>517938</v>
+        <v>513049</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>3193796</v>
+        <v>3192024</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>279856</v>
+        <v>279322</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>1734634</v>
+        <v>1734520</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>224560</v>
+        <v>223938</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>1388827</v>
+        <v>1387467</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>187844546</v>
+        <v>193401378</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>182916223</v>
+        <v>184277421</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>94147763</v>
+        <v>95064013</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>586618726</v>
+        <v>586187715</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1727240</v>
+        <v>1745480</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>10757865</v>
+        <v>10754751</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1565508</v>
+        <v>1575182</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>9718158</v>
+        <v>9716566</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>83585790</v>
+        <v>84041234</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>520105782</v>
+        <v>520718832</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1799009</v>
+        <v>1790634</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>11110675</v>
+        <v>11108697</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>781569</v>
+        <v>782487</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>4854354</v>
+        <v>4860047</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2814019</v>
+        <v>2786655</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>17360822</v>
+        <v>17356097</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1232882</v>
+        <v>1226236</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>7629814</v>
+        <v>7636437</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4838065</v>
+        <v>4790657</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>29843509</v>
+        <v>29847788</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>90258</v>
+        <v>89555</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>629870</v>
+        <v>630119</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2544323</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>15820443</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1699422</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>10545465</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>127316400</v>
+        <v>137580394</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>113780587</v>
+        <v>114839071</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>111430384</v>
+        <v>112475091</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>693837355</v>
+        <v>693751839</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2350203</v>
+        <v>2363980</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>14582510</v>
+        <v>14570280</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>4277955</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>26370034</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1367731</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>8439898</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>853434</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>5275772</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>1021971</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>6331637</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>764797</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>4748953</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>508894</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>3165885</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>423537</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>2637985</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1960330</v>
+        <v>1949684</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>12137916</v>
+        <v>12146741</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1520758</v>
+        <v>1504836</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>9373100</v>
+        <v>9368725</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1232175</v>
+        <v>1227690</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>7631751</v>
+        <v>7632565</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>9324459</v>
+        <v>9281545</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>57629024</v>
+        <v>57583176</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>349706</v>
+        <v>392188</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>2449955</v>
+        <v>2428017</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>669143</v>
+        <v>671897</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>4690852</v>
+        <v>4688602</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>758928</v>
+        <v>671897</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>5321648</v>
+        <v>4688602</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>89564</v>
+        <v>90466</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>629982</v>
+        <v>629814</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>343741</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>2393494</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>747844</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>4615676</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>228539</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>1596071</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171038</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>1197204</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>284443</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>1995536</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>1059969</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>6595531</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>151246</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1064334</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>113402</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>798200</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>189121</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>1330195</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>132577</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>931015</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94888</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>664921</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>76078</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>531876</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>57175</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>398880</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>60528146</v>
+        <v>58350125</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>70055339</v>
+        <v>65412475</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>427731</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>2637127</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>95370</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>664949</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>149555</v>
+        <v>150320</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1049815</v>
+        <v>1050062</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>60378591</v>
+        <v>58627536</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5291130</v>
+        <v>5288259</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>37080957</v>
+        <v>37110333</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>55087461</v>
+        <v>53339277</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>55087461</v>
+        <v>53339277</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>55087461</v>
+        <v>53339277</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>55087461</v>
+        <v>53339277</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>55087461</v>
+        <v>53339277</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
